--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.43516713305556</v>
+        <v>3.483214659121529</v>
       </c>
       <c r="D2" t="n">
-        <v>21.64905592410667</v>
+        <v>3.517971587667335</v>
       </c>
       <c r="E2" t="n">
-        <v>6.539770237053824</v>
+        <v>1.062712663521246</v>
       </c>
       <c r="F2" t="n">
-        <v>6.523180675835941</v>
+        <v>1.06001685982334</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.56263056847492</v>
+        <v>1.878927467377174</v>
       </c>
       <c r="D3" t="n">
-        <v>11.03552707514811</v>
+        <v>1.793273149711568</v>
       </c>
       <c r="E3" t="n">
-        <v>6.539770237053824</v>
+        <v>1.062712663521246</v>
       </c>
       <c r="F3" t="n">
-        <v>6.523180675835941</v>
+        <v>1.06001685982334</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.573769893800421</v>
+        <v>0.9057376077425684</v>
       </c>
       <c r="D4" t="n">
-        <v>5.998296062058756</v>
+        <v>0.9747231100845479</v>
       </c>
       <c r="E4" t="n">
-        <v>6.539770237053824</v>
+        <v>1.062712663521246</v>
       </c>
       <c r="F4" t="n">
-        <v>6.523180675835941</v>
+        <v>1.06001685982334</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
